--- a/courseware_lowcode/labs_lowcode/Lab07-technical-indicators/Lab07_Results.xlsx
+++ b/courseware_lowcode/labs_lowcode/Lab07-technical-indicators/Lab07_Results.xlsx
@@ -520,7 +520,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning 101 for Financial Trading | FSE-DAT-3019-1.1 | Version 2.3. Run each backtest in the lab manual (Alpaca costs, next-bar-open fills, Benchmark = the same symbol), then type the results into the yellow cells. Percentages: type 7.62% (or 0.0762).</t>
+          <t>Machine Learning 101 for Financial Trading | FSE-DAT-3019-1.1 | Version 2.4. Run each backtest in the lab manual (Alpaca costs, next-bar-open fills, Benchmark = the same symbol), then type the results into the yellow cells. Percentages: type 7.62% (or 0.0762).</t>
         </is>
       </c>
     </row>

--- a/courseware_lowcode/labs_lowcode/Lab07-technical-indicators/Lab07_Results.xlsx
+++ b/courseware_lowcode/labs_lowcode/Lab07-technical-indicators/Lab07_Results.xlsx
@@ -520,7 +520,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning 101 for Financial Trading | FSE-DAT-3019-1.1 | Version 2.4. Run each backtest in the lab manual (Alpaca costs, next-bar-open fills, Benchmark = the same symbol), then type the results into the yellow cells. Percentages: type 7.62% (or 0.0762).</t>
+          <t>Machine Learning 101 for Financial Trading | FSE-DAT-3019-1.1 | Version 2.7. Run each backtest in the lab manual (Alpaca costs, next-bar-open fills, Benchmark = the same symbol), then type the results into the yellow cells. Percentages: type 7.62% (or 0.0762).</t>
         </is>
       </c>
     </row>
